--- a/output/pdf_financials_xlsx/ATHA.xlsx
+++ b/output/pdf_financials_xlsx/ATHA.xlsx
@@ -1810,7 +1810,7 @@
         </is>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.416229</v>
       </c>
     </row>
     <row r="93">
@@ -3112,7 +3112,11 @@
           <t>Reserves 628,614 440,784</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/ATHA.xlsx
+++ b/output/pdf_financials_xlsx/ATHA.xlsx
@@ -3280,7 +3280,11 @@
           <t>General and administrative expenses 7(c), 9 742,177 425,353</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
       <c r="E26" s="5" t="n">
         <v>0.43246</v>
       </c>

--- a/output/pdf_financials_xlsx/ATHA.xlsx
+++ b/output/pdf_financials_xlsx/ATHA.xlsx
@@ -1901,10 +1901,8 @@
           <t xml:space="preserve">  Net Income From Continuing Operations</t>
         </is>
       </c>
-      <c r="B99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B99" s="3" t="n">
+        <v>0.612748</v>
       </c>
       <c r="C99" s="1" t="inlineStr">
         <is>
@@ -1918,10 +1916,8 @@
           <t xml:space="preserve">  Cash Flow Depreciation, Depletion and Amortization</t>
         </is>
       </c>
-      <c r="B100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B100" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C100" s="1" t="inlineStr">
         <is>
@@ -1935,10 +1931,8 @@
           <t xml:space="preserve">    Change In Receivables</t>
         </is>
       </c>
-      <c r="B101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B101" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C101" s="1" t="inlineStr">
         <is>
@@ -1952,10 +1946,8 @@
           <t xml:space="preserve">    Change In Inventory</t>
         </is>
       </c>
-      <c r="B102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B102" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C102" s="1" t="inlineStr">
         <is>
@@ -1969,10 +1961,8 @@
           <t xml:space="preserve">    Change In Prepaid Assets</t>
         </is>
       </c>
-      <c r="B103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B103" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C103" s="1" t="inlineStr">
         <is>
@@ -1986,10 +1976,8 @@
           <t xml:space="preserve">    Change In Payables And Accrued Expense</t>
         </is>
       </c>
-      <c r="B104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B104" s="3" t="n">
+        <v>0.0007560000000000001</v>
       </c>
       <c r="C104" s="1" t="inlineStr">
         <is>
@@ -2003,10 +1991,8 @@
           <t xml:space="preserve">    Change In Other Working Capital</t>
         </is>
       </c>
-      <c r="B105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B105" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C105" s="1" t="inlineStr">
         <is>
@@ -2020,10 +2006,8 @@
           <t xml:space="preserve">  Change In Working Capital</t>
         </is>
       </c>
-      <c r="B106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B106" s="3" t="n">
+        <v>0.0007560000000000001</v>
       </c>
       <c r="C106" s="1" t="inlineStr">
         <is>
@@ -2037,10 +2021,8 @@
           <t xml:space="preserve">  Stock Based Compensation</t>
         </is>
       </c>
-      <c r="B107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B107" s="3" t="n">
+        <v>0.026974</v>
       </c>
       <c r="C107" s="1" t="inlineStr">
         <is>
@@ -2054,10 +2036,8 @@
           <t xml:space="preserve">  Asset Impairment Charge</t>
         </is>
       </c>
-      <c r="B108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B108" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C108" s="1" t="inlineStr">
         <is>
@@ -2071,10 +2051,8 @@
           <t xml:space="preserve">  Cash from Discontinued Operating Activities</t>
         </is>
       </c>
-      <c r="B109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B109" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C109" s="1" t="inlineStr">
         <is>
@@ -2088,10 +2066,8 @@
           <t xml:space="preserve">  Cash Flow from Others</t>
         </is>
       </c>
-      <c r="B110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B110" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C110" s="1" t="inlineStr">
         <is>
@@ -2105,10 +2081,8 @@
           <t xml:space="preserve">  Purchase Of Property, Plant, Equipment</t>
         </is>
       </c>
-      <c r="B111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B111" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C111" s="1" t="inlineStr">
         <is>
@@ -2122,10 +2096,8 @@
           <t xml:space="preserve">  Sale Of Property, Plant, Equipment</t>
         </is>
       </c>
-      <c r="B112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B112" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C112" s="1" t="inlineStr">
         <is>
@@ -2139,10 +2111,8 @@
           <t xml:space="preserve">  Purchase Of Business</t>
         </is>
       </c>
-      <c r="B113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B113" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C113" s="1" t="inlineStr">
         <is>
@@ -2156,10 +2126,8 @@
           <t xml:space="preserve">  Purchase Of Investment</t>
         </is>
       </c>
-      <c r="B114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B114" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C114" s="1" t="inlineStr">
         <is>
@@ -2173,10 +2141,8 @@
           <t xml:space="preserve">  Sale Of Investment</t>
         </is>
       </c>
-      <c r="B115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B115" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C115" s="1" t="inlineStr">
         <is>
@@ -2190,10 +2156,8 @@
           <t xml:space="preserve">  Net Intangibles Purchase And Sale</t>
         </is>
       </c>
-      <c r="B116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B116" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C116" s="1" t="inlineStr">
         <is>
@@ -2207,10 +2171,8 @@
           <t xml:space="preserve">  Cash From Discontinued Investing Activities</t>
         </is>
       </c>
-      <c r="B117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B117" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C117" s="1" t="inlineStr">
         <is>
@@ -2224,10 +2186,8 @@
           <t xml:space="preserve">  Cash From Other Investing Activities</t>
         </is>
       </c>
-      <c r="B118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B118" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C118" s="1" t="inlineStr">
         <is>
@@ -2258,10 +2218,8 @@
           <t xml:space="preserve">  Issuance of Stock</t>
         </is>
       </c>
-      <c r="B120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B120" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C120" s="1" t="inlineStr">
         <is>
@@ -2275,10 +2233,8 @@
           <t xml:space="preserve">  Repurchase of Stock</t>
         </is>
       </c>
-      <c r="B121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B121" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C121" s="1" t="inlineStr">
         <is>
@@ -2292,10 +2248,8 @@
           <t xml:space="preserve">  Net Issuance of Preferred Stock</t>
         </is>
       </c>
-      <c r="B122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B122" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C122" s="1" t="inlineStr">
         <is>
@@ -2309,10 +2263,8 @@
           <t xml:space="preserve">    Issuance of Debt</t>
         </is>
       </c>
-      <c r="B123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B123" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C123" s="1" t="inlineStr">
         <is>
@@ -2326,10 +2278,8 @@
           <t xml:space="preserve">    Payments of Debt</t>
         </is>
       </c>
-      <c r="B124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B124" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C124" s="1" t="inlineStr">
         <is>
@@ -2343,10 +2293,8 @@
           <t xml:space="preserve">  Net Issuance of Debt</t>
         </is>
       </c>
-      <c r="B125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B125" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C125" s="1" t="inlineStr">
         <is>
@@ -2360,10 +2308,8 @@
           <t xml:space="preserve">  Cash Flow for Dividends</t>
         </is>
       </c>
-      <c r="B126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B126" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C126" s="1" t="inlineStr">
         <is>
@@ -2394,10 +2340,8 @@
           <t xml:space="preserve">  Other Financing</t>
         </is>
       </c>
-      <c r="B128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B128" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C128" s="1" t="inlineStr">
         <is>
@@ -2411,10 +2355,8 @@
           <t>Cash Flow from Financing</t>
         </is>
       </c>
-      <c r="B129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B129" s="3" t="n">
+        <v>0.6839499999999999</v>
       </c>
       <c r="C129" s="1" t="inlineStr">
         <is>
@@ -2428,10 +2370,8 @@
           <t xml:space="preserve">  Beginning Cash Position</t>
         </is>
       </c>
-      <c r="B130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B130" s="3" t="n">
+        <v>0.015075</v>
       </c>
       <c r="C130" s="1" t="inlineStr">
         <is>
@@ -2445,10 +2385,8 @@
           <t xml:space="preserve">    Effect of Exchange Rate Changes</t>
         </is>
       </c>
-      <c r="B131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B131" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C131" s="1" t="inlineStr">
         <is>
@@ -2462,10 +2400,8 @@
           <t xml:space="preserve">  Net Change in Cash</t>
         </is>
       </c>
-      <c r="B132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B132" s="3" t="n">
+        <v>-0.012267</v>
       </c>
       <c r="C132" s="1" t="inlineStr">
         <is>
@@ -2479,10 +2415,8 @@
           <t>Ending Cash Position</t>
         </is>
       </c>
-      <c r="B133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B133" s="3" t="n">
+        <v>0.002808</v>
       </c>
       <c r="C133" s="1" t="inlineStr">
         <is>
@@ -2496,10 +2430,8 @@
           <t>Capital Expenditure</t>
         </is>
       </c>
-      <c r="B134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B134" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C134" s="1" t="inlineStr">
         <is>
@@ -2535,7 +2467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F59"/>
+  <dimension ref="A1:F87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3241,22 +3173,22 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Cash flows from operating activities</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Exploration, evaluation and project expenses 5 $ 574,136 $ 186,764 $</t>
+          <t>Net income (loss) $ (135,214) $ (636,518) $</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" s="5" t="n">
-        <v>0.351132</v>
+        <v>0.612748</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3267,26 +3199,24 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Revaluation of warrant liability                                                     (186,739)            (27,854)         (1,393,742 )</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>General and administrative expenses 7(c), 9 742,177 425,353</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>GeneralAndAdministrativeExpense</t>
-        </is>
-      </c>
-      <c r="E26" s="5" t="n">
-        <v>0.43246</v>
+          <t>Realized loss on investments 31,825 12,452</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3297,26 +3227,24 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Revaluation of warrant liability                                                     (186,739)            (27,854)         (1,393,742 )</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Total operating expenses 1,316,313 612,117</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>OperatingExpense</t>
-        </is>
-      </c>
-      <c r="E27" s="5" t="n">
-        <v>0.783592</v>
+          <t>Unrealized (gain) loss on investments (997,633) 36,384</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3327,17 +3255,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Net operating loss                                                                 (1,316,313)           (612,117)          (783,592 )</t>
+          <t>Revaluation of warrant liability                                                     (186,739)            (27,854)         (1,393,742 )</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Other income 34,897 –</t>
+          <t>Interest expense 4,692 –</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -3355,22 +3283,26 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Net operating loss                                                                 (1,316,313)           (612,117)          (783,592 )</t>
+          <t>Revaluation of warrant liability                                                     (186,739)            (27,854)         (1,393,742 )</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Interest expense (6,345) (3,419)</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
+          <t>Share based compensation 89,277 24,555</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E29" s="5" t="n">
-        <v>0.002598</v>
+        <v>0.026974</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3381,24 +3313,26 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Net operating loss                                                                 (1,316,313)           (612,117)          (783,592 )</t>
+          <t>Prepaid expense                                                              (447,621)            (87,294)            (13,447 )</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Realized loss on investment (31,825) (12,452)</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Accounts payable and accrued liabilities (59,391) 24,672</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="n">
+        <v>0.0007560000000000001</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3409,24 +3343,22 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Net operating loss                                                                 (1,316,313)           (612,117)          (783,592 )</t>
+          <t>Prepaid expense                                                              (447,621)            (87,294)            (13,447 )</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Unrealized gain (loss) on investment 997,633 (36,384)</t>
+          <t>Accounts payable - related party (6,000) (12,447)</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E31" s="5" t="n">
+        <v>0.070494</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3437,22 +3369,24 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Net operating loss                                                                 (1,316,313)           (612,117)          (783,592 )</t>
+          <t>Cash flows from investing activities</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Revaluation of warrant liability 186,739 27,854</t>
+          <t>Purchase of mineral properties (18,100) (45,000)</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
-      <c r="E32" s="5" t="n">
-        <v>1.393742</v>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3463,22 +3397,28 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Net operating loss                                                                 (1,316,313)           (612,117)          (783,592 )</t>
+          <t>Cash flows from investing activities</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Loss and comprehensive loss $ (135,214) $ (636,518) $</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" s="5" t="n">
-        <v>0.612748</v>
+          <t>Purchase of investments 501,455 71,241</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3489,26 +3429,28 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Net operating loss                                                                 (1,316,313)           (612,117)          (783,592 )</t>
+          <t>Cash flows from investing activities</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Weighted average common shares outstanding – basic 24,508,363 17,757,530</t>
+          <t>Proceeds from sale of investments (36,369) –</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>BasicAverageShares</t>
-        </is>
-      </c>
-      <c r="E34" s="5" t="n">
-        <v>14.459929</v>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3519,26 +3461,24 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Net operating loss                                                                 (1,316,313)           (612,117)          (783,592 )</t>
+          <t>Cash flows from investing activities</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Weighted average common shares outstanding – diluted 24,786,141 17,757,530</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>DilutedAverageShares</t>
-        </is>
-      </c>
-      <c r="E35" s="5" t="n">
-        <v>14.459929</v>
+          <t>Proceeds from sale of rights to mineral property 128,115 –</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3549,22 +3489,28 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Net operating loss                                                                 (1,316,313)           (612,117)          (783,592 )</t>
+          <t>Cash flows from investing activities</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Loss per common share – basic $ (0.01) $ (0.04) $</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr"/>
-      <c r="E36" s="5" t="n">
-        <v>4e-08</v>
+          <t>Net cash used in investing activities 575,101 26,241</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>InvestingCashFlow</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3575,22 +3521,22 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Net operating loss                                                                 (1,316,313)           (612,117)          (783,592 )</t>
+          <t>Cash flows from financing activities</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Income per common share – diluted $ (0.01) $ (0.04) $</t>
+          <t>Loan from related parties (108,111) 20,322</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" s="5" t="n">
-        <v>4e-08</v>
+        <v>0.025</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3601,22 +3547,22 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Shares          Capital        warrants          Deficit           Total</t>
+          <t>Cash flows from financing activities</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>December 31, 2022 13,746,606 $ 16,276,957 $ 389,255 $ (11,702,798) $</t>
+          <t>Deposits for future private placement – (46,000)</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" s="5" t="n">
-        <v>4.963414</v>
+        <v>0.046</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3627,22 +3573,22 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Shares          Capital        warrants          Deficit           Total</t>
+          <t>Payments on notes payable                                                    –                –           (106,210 )</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Private placement, net 1,464,646 744,160 – –</t>
+          <t>Proceeds from private placement of stock, net 3,066,426 904,761</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" s="5" t="n">
-        <v>0.74416</v>
+        <v>0.71916</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3653,22 +3599,26 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Shares          Capital        warrants          Deficit           Total</t>
+          <t>Payments on notes payable                                                    –                –           (106,210 )</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Warrant liability – (525,884) – –</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr"/>
+          <t>Net cash provided by financing activities 2,958,315 879,083</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>FinancingCashFlow</t>
+        </is>
+      </c>
       <c r="E40" s="5" t="n">
-        <v>-0.525884</v>
+        <v>0.6839499999999999</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3679,22 +3629,26 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Shares          Capital        warrants          Deficit           Total</t>
+          <t>Payments on notes payable                                                    –                –           (106,210 )</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Stock based compensation – – 26,974 –</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr"/>
+          <t>Cash, beginning of period 242,082 2,808</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
       <c r="E41" s="5" t="n">
-        <v>0.026974</v>
+        <v>0.015075</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3705,22 +3659,26 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Common stock issued for investment in</t>
+          <t>Payments on notes payable                                                    –                –           (106,210 )</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Common stock issued for investment in securities 1,671,381 496,400 – –</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr"/>
+          <t>Cash, end of period $ 2,068,694 $ 242,082 $</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
       <c r="E42" s="5" t="n">
-        <v>0.4964</v>
+        <v>0.002808</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3731,26 +3689,22 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Common stock issued for investment in</t>
+          <t>Payments on notes payable                                                    –                –           (106,210 )</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Net income – – – 612,748</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Cash $ 244,694 $ 242,082 $</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
       <c r="E43" s="5" t="n">
-        <v>0.612748</v>
+        <v>0.002808</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3761,22 +3715,24 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Common stock issued for investment in</t>
+          <t>Payments on notes payable                                                    –                –           (106,210 )</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>December 31, 2023 16,882,633 $ 16,991,633 $ 416,229 $ (11,090,050) $</t>
+          <t>Cash equivalents 1,824,000 –</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
-      <c r="E44" s="5" t="n">
-        <v>6.317812</v>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3787,22 +3743,26 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Common stock issued for investment in</t>
+          <t>Payments on notes payable                                                    –                –           (106,210 )</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Private placement, net 2,634,343 $ 904,761 $ – $ – $</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr"/>
+          <t>Cash and cash equivalents, end of year $ 2,068,694 $ 242,082 $</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
       <c r="E45" s="5" t="n">
-        <v>0.904761</v>
+        <v>0.002808</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3813,22 +3773,22 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Common stock issued for investment in</t>
+          <t>Noncash investing and financing activities</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Warrant and option liability – (492,405) – –</t>
+          <t>Stock issued to pay off debt 35,601 36,251</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" s="5" t="n">
-        <v>-0.492405</v>
+        <v>0.025</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3839,22 +3799,24 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Common stock issued for investment in</t>
+          <t>Noncash investing and financing activities</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Shares issued to settle debt 99,552 36,251 – –</t>
+          <t>Common stock issued for mineral property 18,135 –</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
-      <c r="E47" s="5" t="n">
-        <v>0.036251</v>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3865,22 +3827,22 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Common stock issued for investment in</t>
+          <t>Noncash investing and financing activities</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Stock based compensation 60,606 – 24,555 –</t>
+          <t>Broker warrants issued 98,553 –</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" s="5" t="n">
-        <v>0.024555</v>
+        <v>0.007953999999999999</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -3891,22 +3853,22 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Common stock issued for investment in</t>
+          <t>Noncash investing and financing activities</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Net loss – – – (636,518)</t>
+          <t>Warrant and option liability recognition 925,115 492,405</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" s="5" t="n">
-        <v>-0.636518</v>
+        <v>0.525884</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -3917,22 +3879,24 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Common stock issued for investment in</t>
+          <t>Noncash investing and financing activities</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>December 31, 2024 19,677,134 $ 17,440,240 $ 440,784 $ (11,726,568) $</t>
+          <t>Common stock received from sale of rights to mineral property 2,059,520 –</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
-      <c r="E50" s="5" t="n">
-        <v>6.154456</v>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3943,22 +3907,24 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Common stock issued for investment in</t>
+          <t>Noncash investing and financing activities</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Private placement, net 7,086,012 $ 2,888,013 $ 98,553 $ – $</t>
+          <t>Shares issued for services 79,860 –</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
-      <c r="E51" s="5" t="n">
-        <v>2.986566</v>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -3969,22 +3935,22 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Common stock issued for investment in</t>
+          <t>Noncash investing and financing activities</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Shares issued for services 223,963 79,860 – –</t>
+          <t>Common stock issued for investment in securities – –</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" s="5" t="n">
-        <v>0.07986</v>
+        <v>0.4964</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4000,19 +3966,17 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Common stock issued for investment in</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Nova shares reissued 4,430,830 – – –</t>
+          <t>Exploration, evaluation and project expenses 5 $ 574,136 $ 186,764 $</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E53" s="5" t="n">
+        <v>0.351132</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4028,17 +3992,21 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Common stock issued for investment in</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Shares issued for mineral property 50,505 18,135 – –</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr"/>
+          <t>General and administrative expenses 7(c), 9 742,177 425,353</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
       <c r="E54" s="5" t="n">
-        <v>0.018135</v>
+        <v>0.43246</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4054,17 +4022,21 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Common stock issued for investment in</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Shares issued for debt 99,091 35,601 – –</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr"/>
+          <t>Total operating expenses 1,316,313 612,117</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
       <c r="E55" s="5" t="n">
-        <v>0.035601</v>
+        <v>0.783592</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4080,17 +4052,19 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Common stock issued for investment in</t>
+          <t>Net operating loss                                                                 (1,316,313)           (612,117)          (783,592 )</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Warrant liability – (925,115) – –</t>
+          <t>Other income 34,897 –</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
-      <c r="E56" s="5" t="n">
-        <v>-0.925115</v>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4106,17 +4080,17 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Common stock issued for investment in</t>
+          <t>Net operating loss                                                                 (1,316,313)           (612,117)          (783,592 )</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Stock based compensation – – 89,277 –</t>
+          <t>Interest expense (6,345) (3,419)</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" s="5" t="n">
-        <v>0.089277</v>
+        <v>0.002598</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4132,17 +4106,19 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Common stock issued for investment in</t>
+          <t>Net operating loss                                                                 (1,316,313)           (612,117)          (783,592 )</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Net loss – – – (135,214)</t>
+          <t>Realized loss on investment (31,825) (12,452)</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
-      <c r="E58" s="5" t="n">
-        <v>-0.135214</v>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4158,19 +4134,763 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
+          <t>Net operating loss                                                                 (1,316,313)           (612,117)          (783,592 )</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Unrealized gain (loss) on investment 997,633 (36,384)</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Net operating loss                                                                 (1,316,313)           (612,117)          (783,592 )</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Revaluation of warrant liability 186,739 27,854</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" s="5" t="n">
+        <v>1.393742</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Net operating loss                                                                 (1,316,313)           (612,117)          (783,592 )</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Loss and comprehensive loss $ (135,214) $ (636,518) $</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" s="5" t="n">
+        <v>0.612748</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Net operating loss                                                                 (1,316,313)           (612,117)          (783,592 )</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Weighted average common shares outstanding – basic 24,508,363 17,757,530</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>BasicAverageShares</t>
+        </is>
+      </c>
+      <c r="E62" s="5" t="n">
+        <v>14.459929</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Net operating loss                                                                 (1,316,313)           (612,117)          (783,592 )</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Weighted average common shares outstanding – diluted 24,786,141 17,757,530</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>DilutedAverageShares</t>
+        </is>
+      </c>
+      <c r="E63" s="5" t="n">
+        <v>14.459929</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Net operating loss                                                                 (1,316,313)           (612,117)          (783,592 )</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Loss per common share – basic $ (0.01) $ (0.04) $</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" s="5" t="n">
+        <v>4e-08</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Net operating loss                                                                 (1,316,313)           (612,117)          (783,592 )</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Income per common share – diluted $ (0.01) $ (0.04) $</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" s="5" t="n">
+        <v>4e-08</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Shares          Capital        warrants          Deficit           Total</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>December 31, 2022 13,746,606 $ 16,276,957 $ 389,255 $ (11,702,798) $</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" s="5" t="n">
+        <v>4.963414</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Shares          Capital        warrants          Deficit           Total</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Private placement, net 1,464,646 744,160 – –</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" s="5" t="n">
+        <v>0.74416</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Shares          Capital        warrants          Deficit           Total</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Warrant liability – (525,884) – –</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" s="5" t="n">
+        <v>-0.525884</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Shares          Capital        warrants          Deficit           Total</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Stock based compensation – – 26,974 –</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" s="5" t="n">
+        <v>0.026974</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
           <t>Common stock issued for investment in</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Common stock issued for investment in securities 1,671,381 496,400 – –</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" s="5" t="n">
+        <v>0.4964</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Common stock issued for investment in</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Net income – – – 612,748</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E71" s="5" t="n">
+        <v>0.612748</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Common stock issued for investment in</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>December 31, 2023 16,882,633 $ 16,991,633 $ 416,229 $ (11,090,050) $</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" s="5" t="n">
+        <v>6.317812</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Common stock issued for investment in</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Private placement, net 2,634,343 $ 904,761 $ – $ – $</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" s="5" t="n">
+        <v>0.904761</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Common stock issued for investment in</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Warrant and option liability – (492,405) – –</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" s="5" t="n">
+        <v>-0.492405</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Common stock issued for investment in</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Shares issued to settle debt 99,552 36,251 – –</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" s="5" t="n">
+        <v>0.036251</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Common stock issued for investment in</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Stock based compensation 60,606 – 24,555 –</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" s="5" t="n">
+        <v>0.024555</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Common stock issued for investment in</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Net loss – – – (636,518)</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr"/>
+      <c r="E77" s="5" t="n">
+        <v>-0.636518</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Common stock issued for investment in</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>December 31, 2024 19,677,134 $ 17,440,240 $ 440,784 $ (11,726,568) $</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr"/>
+      <c r="E78" s="5" t="n">
+        <v>6.154456</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Common stock issued for investment in</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Private placement, net 7,086,012 $ 2,888,013 $ 98,553 $ – $</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr"/>
+      <c r="E79" s="5" t="n">
+        <v>2.986566</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Common stock issued for investment in</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Shares issued for services 223,963 79,860 – –</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr"/>
+      <c r="E80" s="5" t="n">
+        <v>0.07986</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Common stock issued for investment in</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Nova shares reissued 4,430,830 – – –</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr"/>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Common stock issued for investment in</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Shares issued for mineral property 50,505 18,135 – –</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" s="5" t="n">
+        <v>0.018135</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Common stock issued for investment in</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Shares issued for debt 99,091 35,601 – –</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" s="5" t="n">
+        <v>0.035601</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Common stock issued for investment in</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Warrant liability – (925,115) – –</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr"/>
+      <c r="E84" s="5" t="n">
+        <v>-0.925115</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Common stock issued for investment in</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Stock based compensation – – 89,277 –</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr"/>
+      <c r="E85" s="5" t="n">
+        <v>0.089277</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Common stock issued for investment in</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Net loss – – – (135,214)</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr"/>
+      <c r="E86" s="5" t="n">
+        <v>-0.135214</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Common stock issued for investment in</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
         <is>
           <t>December 31, 2025 31,567,535 $ 19,536,734 $ 628,614 $ (11,861,782) $</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr"/>
-      <c r="E59" s="5" t="n">
+      <c r="D87" t="inlineStr"/>
+      <c r="E87" s="5" t="n">
         <v>8.303566</v>
       </c>
-      <c r="F59" t="inlineStr">
+      <c r="F87" t="inlineStr">
         <is>
           <t>-</t>
         </is>
